--- a/data/trans_bre/IP04D$aparatos-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$aparatos-Provincia-trans_bre.xlsx
@@ -584,7 +584,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -632,39 +632,39 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,39; 31,14</t>
+          <t>2,15; 32,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,39; 6,01</t>
+          <t>-13,57; 7,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,42; 10,14</t>
+          <t>-17,15; 9,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,73; 79,34</t>
+          <t>3,52; 85,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-69,25; 58,92</t>
+          <t>-62,49; 74,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-47,2; 41,77</t>
+          <t>-46,2; 36,95</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -712,39 +712,39 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 14,28</t>
+          <t>-6,38; 14,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 16,43</t>
+          <t>-4,46; 16,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 13,39</t>
+          <t>-3,46; 12,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 23,84</t>
+          <t>-9,18; 24,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,37; 59,1</t>
+          <t>-11,56; 58,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 16,92</t>
+          <t>-3,82; 15,85</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,37; 8,16</t>
+          <t>-15,21; 8,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,53; 8,73</t>
+          <t>-14,11; 8,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,15; 15,71</t>
+          <t>-11,32; 15,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,81; 10,98</t>
+          <t>-18,7; 11,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-18,37; 12,4</t>
+          <t>-16,88; 11,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,18; 28,31</t>
+          <t>-16,55; 27,24</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,04; 11,05</t>
+          <t>-17,51; 8,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,23; 14,29</t>
+          <t>-11,48; 13,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-13,9; 22,43</t>
+          <t>-13,46; 21,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,62; 20,97</t>
+          <t>-25,54; 15,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-18,35; 25,96</t>
+          <t>-16,71; 26,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,52; 99,96</t>
+          <t>-29,29; 102,18</t>
         </is>
       </c>
     </row>
@@ -952,39 +952,39 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 22,32</t>
+          <t>-11,34; 23,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,48; 12,25</t>
+          <t>-12,16; 9,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 0,0</t>
+          <t>-8,23; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-17,6; 47,73</t>
+          <t>-17,54; 51,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 14,49</t>
+          <t>-13,03; 11,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 0,0</t>
+          <t>-8,23; 0,0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1032,39 +1032,39 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-23,77; 3,68</t>
+          <t>-23,54; 3,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-17,85; 7,8</t>
+          <t>-17,55; 8,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,5; 17,51</t>
+          <t>-13,72; 18,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-29,11; 4,65</t>
+          <t>-28,89; 4,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-61,46; 53,55</t>
+          <t>-60,8; 52,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-26,48; 52,3</t>
+          <t>-27,77; 57,72</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 9,79</t>
+          <t>-8,02; 9,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,5; 6,52</t>
+          <t>-12,38; 6,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,1; 20,91</t>
+          <t>1,03; 21,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,28; 13,7</t>
+          <t>-10,21; 13,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-21,88; 14,01</t>
+          <t>-21,61; 13,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,18; 131,87</t>
+          <t>5,05; 145,32</t>
         </is>
       </c>
     </row>
@@ -1192,32 +1192,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 15,22</t>
+          <t>-1,8; 15,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 5,34</t>
+          <t>-10,69; 6,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 3,26</t>
+          <t>-5,69; 3,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 38,01</t>
+          <t>-3,96; 37,86</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-16,75; 8,61</t>
+          <t>-15,16; 9,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 3,51</t>
+          <t>-5,94; 4,23</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 6,85</t>
+          <t>-1,7; 6,83</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 3,28</t>
+          <t>-5,33; 3,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 10,58</t>
+          <t>-0,98; 10,02</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 11,36</t>
+          <t>-2,67; 11,48</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 6,34</t>
+          <t>-9,54; 6,3</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 19,01</t>
+          <t>-1,53; 17,69</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$aparatos-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$aparatos-Provincia-trans_bre.xlsx
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,15; 32,05</t>
+          <t>2,76; 32,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,57; 7,05</t>
+          <t>-14,21; 5,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,15; 9,15</t>
+          <t>-17,71; 10,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,52; 85,32</t>
+          <t>5,2; 83,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-62,49; 74,65</t>
+          <t>-65,36; 61,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-46,2; 36,95</t>
+          <t>-45,59; 41,41</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 14,52</t>
+          <t>-7,6; 14,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 16,63</t>
+          <t>-4,33; 17,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 12,8</t>
+          <t>-3,6; 13,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,18; 24,07</t>
+          <t>-10,5; 24,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 58,24</t>
+          <t>-11,48; 61,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 15,85</t>
+          <t>-4,28; 16,59</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,21; 8,03</t>
+          <t>-14,79; 8,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,11; 8,78</t>
+          <t>-15,48; 8,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 15,05</t>
+          <t>-10,96; 17,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,7; 11,14</t>
+          <t>-17,89; 11,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-16,88; 11,72</t>
+          <t>-18,49; 11,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,55; 27,24</t>
+          <t>-15,86; 33,67</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,51; 8,77</t>
+          <t>-16,35; 10,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 13,91</t>
+          <t>-11,68; 13,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-13,46; 21,65</t>
+          <t>-13,05; 21,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-25,54; 15,63</t>
+          <t>-24,56; 19,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-16,71; 26,53</t>
+          <t>-17,2; 26,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,29; 102,18</t>
+          <t>-29,15; 108,11</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 23,48</t>
+          <t>-14,08; 21,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,16; 9,84</t>
+          <t>-12,72; 10,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 0,0</t>
+          <t>-8,17; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-17,54; 51,77</t>
+          <t>-21,71; 47,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 11,69</t>
+          <t>-13,82; 13,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 0,0</t>
+          <t>-8,17; 0,0</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-23,54; 3,1</t>
+          <t>-22,92; 3,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-17,55; 8,1</t>
+          <t>-17,06; 8,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 18,08</t>
+          <t>-12,86; 18,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-28,89; 4,5</t>
+          <t>-28,44; 4,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-60,8; 52,98</t>
+          <t>-58,44; 58,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-27,77; 57,72</t>
+          <t>-27,07; 52,88</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 9,11</t>
+          <t>-7,43; 9,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,38; 6,44</t>
+          <t>-13,86; 6,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,03; 21,21</t>
+          <t>1,35; 20,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 13,11</t>
+          <t>-9,38; 14,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-21,61; 13,54</t>
+          <t>-23,41; 13,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,05; 145,32</t>
+          <t>4,81; 134,02</t>
         </is>
       </c>
     </row>
@@ -1192,32 +1192,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 15,05</t>
+          <t>-1,92; 15,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 6,12</t>
+          <t>-10,8; 5,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 3,9</t>
+          <t>-5,37; 4,22</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 37,86</t>
+          <t>-4,46; 39,75</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,16; 9,99</t>
+          <t>-15,55; 9,43</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 4,23</t>
+          <t>-5,63; 4,59</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 6,83</t>
+          <t>-1,89; 6,38</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 3,13</t>
+          <t>-5,19; 3,16</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 10,02</t>
+          <t>-1,82; 10,24</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 11,48</t>
+          <t>-2,95; 10,56</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,54; 6,3</t>
+          <t>-9,56; 6,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 17,69</t>
+          <t>-3,23; 18,16</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$aparatos-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$aparatos-Provincia-trans_bre.xlsx
@@ -518,8 +518,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que no dispone de instalación de calefacción en su vivienda pero sí tiene aparatos de calefacción</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -604,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-3,62</t>
+          <t>0,27</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -619,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-11,3%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -632,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,76; 32,05</t>
+          <t>2,39; 31,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,21; 5,52</t>
+          <t>-13,39; 6,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,71; 10,39</t>
+          <t>-14,01; 13,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,2; 83,25</t>
+          <t>3,73; 79,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-65,36; 61,91</t>
+          <t>-69,25; 58,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-45,59; 41,41</t>
+          <t>-34,87; 54,0</t>
         </is>
       </c>
     </row>
@@ -684,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,66</t>
+          <t>2,76</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -699,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -712,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 14,75</t>
+          <t>-6,06; 14,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 17,62</t>
+          <t>-5,45; 16,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 13,52</t>
+          <t>-4,33; 10,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,5; 24,6</t>
+          <t>-8,79; 23,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 61,55</t>
+          <t>-14,37; 59,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 16,59</t>
+          <t>-4,85; 13,19</t>
         </is>
       </c>
     </row>
@@ -764,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,68</t>
+          <t>3,22</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -779,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -792,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,79; 8,63</t>
+          <t>-15,37; 8,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,48; 8,22</t>
+          <t>-15,53; 8,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 17,38</t>
+          <t>-10,38; 16,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,89; 11,37</t>
+          <t>-18,81; 10,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-18,49; 11,61</t>
+          <t>-18,37; 12,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,86; 33,67</t>
+          <t>-14,99; 30,0</t>
         </is>
       </c>
     </row>
@@ -844,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4,06</t>
+          <t>2,03</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -859,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -872,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,35; 10,31</t>
+          <t>-16,04; 11,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 13,77</t>
+          <t>-12,23; 14,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 21,75</t>
+          <t>-16,26; 19,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-24,56; 19,16</t>
+          <t>-23,62; 20,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-17,2; 26,49</t>
+          <t>-18,35; 25,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-29,15; 108,11</t>
+          <t>-35,73; 87,27</t>
         </is>
       </c>
     </row>
@@ -924,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,6</t>
+          <t>-1,55</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -939,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,6%</t>
+          <t>-1,55%</t>
         </is>
       </c>
     </row>
@@ -952,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,08; 21,83</t>
+          <t>-11,68; 22,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,72; 10,88</t>
+          <t>-10,48; 12,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 0,0</t>
+          <t>-7,81; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,71; 47,2</t>
+          <t>-17,6; 47,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,82; 13,05</t>
+          <t>-11,35; 14,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 0,0</t>
+          <t>-7,81; 0,0</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2,26</t>
+          <t>1,36</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1019,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-22,92; 3,57</t>
+          <t>-23,77; 3,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-17,06; 8,36</t>
+          <t>-17,85; 7,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 18,43</t>
+          <t>-14,51; 16,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-28,44; 4,92</t>
+          <t>-29,11; 4,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-58,44; 58,6</t>
+          <t>-61,46; 53,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-27,07; 52,88</t>
+          <t>-28,52; 48,78</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10,61</t>
+          <t>8,78</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1099,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>45,41%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 9,66</t>
+          <t>-7,2; 9,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,86; 6,15</t>
+          <t>-12,5; 6,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,35; 20,7</t>
+          <t>-0,26; 17,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 14,14</t>
+          <t>-9,28; 13,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-23,41; 13,08</t>
+          <t>-21,88; 14,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,81; 134,02</t>
+          <t>-2,14; 116,47</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1166,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-0,92</t>
+          <t>-0,9</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1179,7 +1181,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-0,97%</t>
+          <t>-0,95%</t>
         </is>
       </c>
     </row>
@@ -1192,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 15,23</t>
+          <t>-2,89; 15,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 5,74</t>
+          <t>-11,65; 5,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 4,22</t>
+          <t>-5,95; 3,12</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 39,75</t>
+          <t>-6,01; 38,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,55; 9,43</t>
+          <t>-16,75; 8,61</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 4,59</t>
+          <t>-6,2; 3,33</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1246,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3,91</t>
+          <t>2,31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1259,7 +1261,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 6,38</t>
+          <t>-1,47; 6,85</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 3,16</t>
+          <t>-5,23; 3,28</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 10,24</t>
+          <t>-2,29; 7,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 10,56</t>
+          <t>-2,35; 11,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 6,12</t>
+          <t>-9,61; 6,34</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 18,16</t>
+          <t>-3,68; 12,79</t>
         </is>
       </c>
     </row>
